--- a/jira_clone/prompt_study.xlsx
+++ b/jira_clone/prompt_study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3239379-045B-4F40-8EC3-79820B5D11D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E695AD39-53B5-4478-89A7-284FBE56C313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="110">
   <si>
     <t>Prompt Study Workbook</t>
   </si>
@@ -361,6 +361,107 @@
   <si>
     <t>Finally update the ManageTicketTracking.js to mention that ticket is on the final status use isEndStatus ENCAPSULATE IN SPRINTTICKETS STATE</t>
   </si>
+  <si>
+    <t xml:space="preserve">in @force-app/main/default/lwc/manageTicketTracking/manageTicketTracking.js , for _loadData() method  Todo : implement the todo in this line :   // compare the id of the tickettype in sprintTickets with ticketTypes Then add  the sprintTickets ticketTypeName and the same for association create for each of them a method in the util @force-app/main/default/lwc/aoTicketItem/ticketUtils.js  </t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>excellent</t>
+  </si>
+  <si>
+    <t>sprint1-task9
+sprint1-task10</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>Create a card list with a + button in the header to add a new row inline, and an expand/collapse button on header to reveal more rows. Minimal flat design, compact rows, no specific app style.</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>create Ticket Link backEnd + FrontEnd</t>
+  </si>
+  <si>
+    <t>see the file P011.txt</t>
+  </si>
+  <si>
+    <t>see the file P012.txt</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>P013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+- A "+ Create linked work item" text button to create a brand new linked item.
+						00.02.05.02 : 
+							- when the link button is clicked dispatch event should be send from the child to the pather , 
+							- pather(ManageTicketTracking.js is the pather) it should handle the  event and send a apex request to create a new ticket Link 
+							sequence : 
+							 - controller will receive the request 
+							 - controller use DomainCorrectness to check intgrity 
+							 - controller will call the ticketService to save the new Ticket Link
+							- Once the response is done in .then update the list  of the ticketLink : linkedToItems  state in the pather that we should already passed to the ticketLinkTo component 
+										</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00.02.05.02 in manageTicketTracking requirement file : </t>
+  </si>
+  <si>
+    <t>@force-app/main/default/classes/domain/DomainCompleteValidator.cls  add this new rules add DomainCompleteValidator check that we cannot do a transition from isEnd status 
+add DomainCompleteValidator check that we cannot do a transition to todo and in  @force-app/main/default/classes/domain/WorkflowService.cls  in createWorkflowTransition calkl this new rules</t>
+  </si>
+  <si>
+    <t>P014</t>
+  </si>
+  <si>
+    <t>P015</t>
+  </si>
+  <si>
+    <t>`@force-app/main/default/classes/controller/manageTicketTracking/  
+_loadData method 
+ loadManageTicketTrackingPage call 
+ // Todo this should be calculated 
+                // Todo check the response.statuses that have isEnd true when the ticket hit this status so it was in the end status 
+based on the return  Map&lt;String, Object&gt; data = new Map&lt;String, Object&gt;{
+                'status'              =&gt; statuses,
+                'workflows'           =&gt; workflows,
+                'sprint_tickets'      =&gt; sprintTickets,
+                'members'             =&gt; members,
+                'ticketTypes'         =&gt; ticketTypes,
+                'sprint'              =&gt; sprint
+            };
+where the status have the isEnd and is Start</t>
+  </si>
+  <si>
+    <t>@force-app/main/default/classes/controller/manageTicketTracking/  
+_loadData method 
+ loadManageTicketTrackingPage call 
+ // Todo this should be calculated 
+                // Todo check the response.statuses that have isEnd true when the ticket hit this status so it was in the end status 
+based on the return  Map&lt;String, Object&gt; data = new Map&lt;String, Object&gt;{
+                'status'              =&gt; statuses,
+                'workflows'           =&gt; workflows,
+                'sprint_tickets'      =&gt; sprintTickets,
+                'members'             =&gt; members,
+                'ticketTypes'         =&gt; ticketTypes,
+                'sprint'              =&gt; sprint
+            };
+where the status have the isEnd and is Start</t>
+  </si>
+  <si>
+    <t>js</t>
+  </si>
+  <si>
+    <t>P016</t>
+  </si>
 </sst>
 </file>
 
@@ -371,7 +472,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\-#,##0.0;\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,6 +522,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF85B6FF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -448,7 +555,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -471,17 +578,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -538,6 +651,18 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,119 +937,119 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="2:3" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -948,229 +1073,229 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="6">
         <f>COUNTIF(Prompts!$B$4:$B$1000,A4)</f>
         <v>3</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="6">
         <f>SUMIF(Prompts!$B$4:$B$1000,A4,Prompts!$F$4:$F$1000)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="7">
         <f>IFERROR(E4/D4,0)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="11" t="str">
+      <c r="G4" s="8" t="str">
         <f>IF(D4=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress"))</f>
         <v>Complete</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="12" t="str">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="9" t="str">
         <f>IF(A7="","",COUNTIF(Prompts!$B$4:$B$1000,A7))</f>
         <v/>
       </c>
-      <c r="E7" s="12" t="str">
+      <c r="E7" s="9" t="str">
         <f>IF(A7="","",SUMIF(Prompts!$B$4:$B$1000,A7,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F7" s="13" t="str">
+      <c r="F7" s="10" t="str">
         <f t="shared" ref="F7:F13" si="0">IF(OR(A7="",D7=0),"",E7/D7)</f>
         <v/>
       </c>
-      <c r="G7" s="8" t="str">
+      <c r="G7" s="5" t="str">
         <f>IF(A7="","",IF(D7=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="12" t="str">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="9" t="str">
         <f>IF(A8="","",COUNTIF(Prompts!$B$4:$B$1000,A8))</f>
         <v/>
       </c>
-      <c r="E8" s="12" t="str">
+      <c r="E8" s="9" t="str">
         <f>IF(A8="","",SUMIF(Prompts!$B$4:$B$1000,A8,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F8" s="13" t="str">
+      <c r="F8" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G8" s="8" t="str">
+      <c r="G8" s="5" t="str">
         <f>IF(A8="","",IF(D8=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="12" t="str">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="9" t="str">
         <f>IF(A9="","",COUNTIF(Prompts!$B$4:$B$1000,A9))</f>
         <v/>
       </c>
-      <c r="E9" s="12" t="str">
+      <c r="E9" s="9" t="str">
         <f>IF(A9="","",SUMIF(Prompts!$B$4:$B$1000,A9,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F9" s="13" t="str">
+      <c r="F9" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G9" s="8" t="str">
+      <c r="G9" s="5" t="str">
         <f>IF(A9="","",IF(D9=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="12" t="str">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="9" t="str">
         <f>IF(A10="","",COUNTIF(Prompts!$B$4:$B$1000,A10))</f>
         <v/>
       </c>
-      <c r="E10" s="12" t="str">
+      <c r="E10" s="9" t="str">
         <f>IF(A10="","",SUMIF(Prompts!$B$4:$B$1000,A10,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F10" s="13" t="str">
+      <c r="F10" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="8" t="str">
+      <c r="G10" s="5" t="str">
         <f>IF(A10="","",IF(D10=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="12" t="str">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="9" t="str">
         <f>IF(A11="","",COUNTIF(Prompts!$B$4:$B$1000,A11))</f>
         <v/>
       </c>
-      <c r="E11" s="12" t="str">
+      <c r="E11" s="9" t="str">
         <f>IF(A11="","",SUMIF(Prompts!$B$4:$B$1000,A11,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F11" s="13" t="str">
+      <c r="F11" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="8" t="str">
+      <c r="G11" s="5" t="str">
         <f>IF(A11="","",IF(D11=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="12" t="str">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="9" t="str">
         <f>IF(A12="","",COUNTIF(Prompts!$B$4:$B$1000,A12))</f>
         <v/>
       </c>
-      <c r="E12" s="12" t="str">
+      <c r="E12" s="9" t="str">
         <f>IF(A12="","",SUMIF(Prompts!$B$4:$B$1000,A12,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F12" s="13" t="str">
+      <c r="F12" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="8" t="str">
+      <c r="G12" s="5" t="str">
         <f>IF(A12="","",IF(D12=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="12" t="str">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="9" t="str">
         <f>IF(A13="","",COUNTIF(Prompts!$B$4:$B$1000,A13))</f>
         <v/>
       </c>
-      <c r="E13" s="12" t="str">
+      <c r="E13" s="9" t="str">
         <f>IF(A13="","",SUMIF(Prompts!$B$4:$B$1000,A13,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="F13" s="13" t="str">
+      <c r="F13" s="10" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G13" s="8" t="str">
+      <c r="G13" s="5" t="str">
         <f>IF(A13="","",IF(D13=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
@@ -1190,7 +1315,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="43.109375" customWidth="1"/>
     <col min="4" max="4" width="60" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
@@ -1199,392 +1324,456 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="5" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="238.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="5" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="241.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="204" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="20" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="132" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="23" t="s">
+      <c r="C9" s="5"/>
+      <c r="D9" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="23" t="s">
+      <c r="C10" s="5"/>
+      <c r="D10" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="8"/>
+      <c r="H10" s="5" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="23" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="8" t="s">
+      <c r="G11" s="8"/>
+      <c r="H11" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="8"/>
+    <row r="12" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="20" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="8"/>
-    </row>
-    <row r="21" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="8"/>
+      <c r="A15" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="394.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" ht="176.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" ht="205.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" ht="319.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="27"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="8"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="8"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="8"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F26" s="14"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F27" s="14"/>
+      <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F28" s="14"/>
+      <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F29" s="14"/>
+      <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F30" s="14"/>
+      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F31" s="14"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F32" s="14"/>
+      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="6:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F33" s="14"/>
+      <c r="F33" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1632,471 +1821,471 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="13">
         <f>COUNTA(Prompts!A4:A1000)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="13">
         <f>COUNTA(Groups!A4:A50)</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <f>SUM(Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <f>IFERROR(SUM(Prompts!F4:F1000)/COUNTIF(Prompts!F4:F1000,"&gt;0"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <f>IFERROR(MAX(Prompts!F4:F1000),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <f>IFERROR(SMALL(Prompts!F4:F1000,COUNTIF(Prompts!F4:F1000,0)+1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="14">
         <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Success")/COUNTA(Prompts!A4:A1000),0)</f>
-        <v>0.625</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Failed")/COUNTA(Prompts!A4:A1000),0)</f>
-        <v>0.25</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="15">
         <f>COUNTIF(Prompts!E4:E1000,A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="15">
         <f>SUMIF(Prompts!E4:E1000,A16,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="15">
         <f>COUNTIF(Prompts!E4:E1000,A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="15">
         <f>SUMIF(Prompts!E4:E1000,A17,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="15">
         <f>COUNTIF(Prompts!E4:E1000,A18)</f>
-        <v>5</v>
-      </c>
-      <c r="C18" s="18">
+        <v>9</v>
+      </c>
+      <c r="C18" s="15">
         <f>SUMIF(Prompts!E4:E1000,A18,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="15">
         <f>COUNTIF(Prompts!E4:E1000,A19)</f>
-        <v>2</v>
-      </c>
-      <c r="C19" s="18">
+        <v>3</v>
+      </c>
+      <c r="C19" s="15">
         <f>SUMIF(Prompts!E4:E1000,A19,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="15">
         <f>COUNTIF(Prompts!E4:E1000,A20)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="15">
         <f>SUMIF(Prompts!E4:E1000,A20,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="20">
+      <c r="B21" s="17">
         <f>SUM(B16:B20)</f>
-        <v>7</v>
-      </c>
-      <c r="C21" s="20">
+        <v>12</v>
+      </c>
+      <c r="C21" s="17">
         <f>SUM(C16:C20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11" t="str">
+      <c r="A26" s="8" t="str">
         <f>IF(Groups!A4="","",Groups!A4)</f>
         <v>G001</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="5">
         <f>IF(Groups!A4="","",Groups!B4)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="15">
         <f>IF(Groups!A4="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A4))</f>
         <v>3</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="15">
         <f>IF(Groups!A4="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$F$4:$F$1000))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="15">
         <f>IF(Groups!A4="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$E$4:$E$1000,"Success"))</f>
         <v>3</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="18">
         <f t="shared" ref="F26:F35" si="0">IFERROR(E26/C26,"")</f>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="str">
+      <c r="A27" s="8" t="str">
         <f>IF(Groups!A5="","",Groups!A5)</f>
         <v>G002</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="5">
         <f>IF(Groups!A5="","",Groups!B5)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="15">
         <f>IF(Groups!A5="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A5))</f>
         <v>3</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="15">
         <f>IF(Groups!A5="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$F$4:$F$1000))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="15">
         <f>IF(Groups!A5="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$E$4:$E$1000,"Success"))</f>
         <v>2</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="18">
         <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11" t="str">
+      <c r="A28" s="8" t="str">
         <f>IF(Groups!A6="","",Groups!A6)</f>
         <v/>
       </c>
-      <c r="B28" s="8" t="str">
+      <c r="B28" s="5" t="str">
         <f>IF(Groups!A6="","",Groups!B6)</f>
         <v/>
       </c>
-      <c r="C28" s="18" t="str">
+      <c r="C28" s="15" t="str">
         <f>IF(Groups!A6="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A6))</f>
         <v/>
       </c>
-      <c r="D28" s="18" t="str">
+      <c r="D28" s="15" t="str">
         <f>IF(Groups!A6="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E28" s="18" t="str">
+      <c r="E28" s="15" t="str">
         <f>IF(Groups!A6="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F28" s="21" t="str">
+      <c r="F28" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="11" t="str">
+      <c r="A29" s="8" t="str">
         <f>IF(Groups!A7="","",Groups!A7)</f>
         <v/>
       </c>
-      <c r="B29" s="8" t="str">
+      <c r="B29" s="5" t="str">
         <f>IF(Groups!A7="","",Groups!B7)</f>
         <v/>
       </c>
-      <c r="C29" s="18" t="str">
+      <c r="C29" s="15" t="str">
         <f>IF(Groups!A7="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A7))</f>
         <v/>
       </c>
-      <c r="D29" s="18" t="str">
+      <c r="D29" s="15" t="str">
         <f>IF(Groups!A7="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E29" s="18" t="str">
+      <c r="E29" s="15" t="str">
         <f>IF(Groups!A7="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F29" s="21" t="str">
+      <c r="F29" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="11" t="str">
+      <c r="A30" s="8" t="str">
         <f>IF(Groups!A8="","",Groups!A8)</f>
         <v/>
       </c>
-      <c r="B30" s="8" t="str">
+      <c r="B30" s="5" t="str">
         <f>IF(Groups!A8="","",Groups!B8)</f>
         <v/>
       </c>
-      <c r="C30" s="18" t="str">
+      <c r="C30" s="15" t="str">
         <f>IF(Groups!A8="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A8))</f>
         <v/>
       </c>
-      <c r="D30" s="18" t="str">
+      <c r="D30" s="15" t="str">
         <f>IF(Groups!A8="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E30" s="18" t="str">
+      <c r="E30" s="15" t="str">
         <f>IF(Groups!A8="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F30" s="21" t="str">
+      <c r="F30" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="11" t="str">
+      <c r="A31" s="8" t="str">
         <f>IF(Groups!A9="","",Groups!A9)</f>
         <v/>
       </c>
-      <c r="B31" s="8" t="str">
+      <c r="B31" s="5" t="str">
         <f>IF(Groups!A9="","",Groups!B9)</f>
         <v/>
       </c>
-      <c r="C31" s="18" t="str">
+      <c r="C31" s="15" t="str">
         <f>IF(Groups!A9="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A9))</f>
         <v/>
       </c>
-      <c r="D31" s="18" t="str">
+      <c r="D31" s="15" t="str">
         <f>IF(Groups!A9="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E31" s="18" t="str">
+      <c r="E31" s="15" t="str">
         <f>IF(Groups!A9="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F31" s="21" t="str">
+      <c r="F31" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="11" t="str">
+      <c r="A32" s="8" t="str">
         <f>IF(Groups!A10="","",Groups!A10)</f>
         <v/>
       </c>
-      <c r="B32" s="8" t="str">
+      <c r="B32" s="5" t="str">
         <f>IF(Groups!A10="","",Groups!B10)</f>
         <v/>
       </c>
-      <c r="C32" s="18" t="str">
+      <c r="C32" s="15" t="str">
         <f>IF(Groups!A10="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A10))</f>
         <v/>
       </c>
-      <c r="D32" s="18" t="str">
+      <c r="D32" s="15" t="str">
         <f>IF(Groups!A10="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E32" s="18" t="str">
+      <c r="E32" s="15" t="str">
         <f>IF(Groups!A10="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F32" s="21" t="str">
+      <c r="F32" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="11" t="str">
+      <c r="A33" s="8" t="str">
         <f>IF(Groups!A11="","",Groups!A11)</f>
         <v/>
       </c>
-      <c r="B33" s="8" t="str">
+      <c r="B33" s="5" t="str">
         <f>IF(Groups!A11="","",Groups!B11)</f>
         <v/>
       </c>
-      <c r="C33" s="18" t="str">
+      <c r="C33" s="15" t="str">
         <f>IF(Groups!A11="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A11))</f>
         <v/>
       </c>
-      <c r="D33" s="18" t="str">
+      <c r="D33" s="15" t="str">
         <f>IF(Groups!A11="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E33" s="18" t="str">
+      <c r="E33" s="15" t="str">
         <f>IF(Groups!A11="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F33" s="21" t="str">
+      <c r="F33" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11" t="str">
+      <c r="A34" s="8" t="str">
         <f>IF(Groups!A12="","",Groups!A12)</f>
         <v/>
       </c>
-      <c r="B34" s="8" t="str">
+      <c r="B34" s="5" t="str">
         <f>IF(Groups!A12="","",Groups!B12)</f>
         <v/>
       </c>
-      <c r="C34" s="18" t="str">
+      <c r="C34" s="15" t="str">
         <f>IF(Groups!A12="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A12))</f>
         <v/>
       </c>
-      <c r="D34" s="18" t="str">
+      <c r="D34" s="15" t="str">
         <f>IF(Groups!A12="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E34" s="18" t="str">
+      <c r="E34" s="15" t="str">
         <f>IF(Groups!A12="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F34" s="21" t="str">
+      <c r="F34" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11" t="str">
+      <c r="A35" s="8" t="str">
         <f>IF(Groups!A13="","",Groups!A13)</f>
         <v/>
       </c>
-      <c r="B35" s="8" t="str">
+      <c r="B35" s="5" t="str">
         <f>IF(Groups!A13="","",Groups!B13)</f>
         <v/>
       </c>
-      <c r="C35" s="18" t="str">
+      <c r="C35" s="15" t="str">
         <f>IF(Groups!A13="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A13))</f>
         <v/>
       </c>
-      <c r="D35" s="18" t="str">
+      <c r="D35" s="15" t="str">
         <f>IF(Groups!A13="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E35" s="18" t="str">
+      <c r="E35" s="15" t="str">
         <f>IF(Groups!A13="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F35" s="21" t="str">
+      <c r="F35" s="18" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>

--- a/jira_clone/prompt_study.xlsx
+++ b/jira_clone/prompt_study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E695AD39-53B5-4478-89A7-284FBE56C313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB665309-45F8-4764-8F89-40C38579A15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="113">
   <si>
     <t>Prompt Study Workbook</t>
   </si>
@@ -457,10 +457,19 @@
 where the status have the isEnd and is Start</t>
   </si>
   <si>
-    <t>js</t>
-  </si>
-  <si>
     <t>P016</t>
+  </si>
+  <si>
+    <t>`@force-app/main/default/objects/Sprint__c/ Please add totalStoryPoint and totalEndedStoryPoint</t>
+  </si>
+  <si>
+    <t>P017</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>task 19</t>
   </si>
 </sst>
 </file>
@@ -593,7 +602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -656,12 +665,15 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1073,15 +1085,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1115,11 +1127,11 @@
         <v>70</v>
       </c>
       <c r="D4" s="6">
-        <f>COUNTIF(Prompts!$B$4:$B$1000,A4)</f>
+        <f>COUNTIF(Prompts!$B$4:$B$999,A4)</f>
         <v>3</v>
       </c>
       <c r="E4" s="6">
-        <f>SUMIF(Prompts!$B$4:$B$1000,A4,Prompts!$F$4:$F$1000)</f>
+        <f>SUMIF(Prompts!$B$4:$B$999,A4,Prompts!$F$4:$F$999)</f>
         <v>0</v>
       </c>
       <c r="F4" s="7">
@@ -1127,7 +1139,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="8" t="str">
-        <f>IF(D4=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress"))</f>
+        <f>IF(D4=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A4,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A4,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A4,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress"))</f>
         <v>Complete</v>
       </c>
     </row>
@@ -1158,11 +1170,11 @@
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="9" t="str">
-        <f>IF(A7="","",COUNTIF(Prompts!$B$4:$B$1000,A7))</f>
+        <f>IF(A7="","",COUNTIF(Prompts!$B$4:$B$999,A7))</f>
         <v/>
       </c>
       <c r="E7" s="9" t="str">
-        <f>IF(A7="","",SUMIF(Prompts!$B$4:$B$1000,A7,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A7="","",SUMIF(Prompts!$B$4:$B$999,A7,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F7" s="10" t="str">
@@ -1170,7 +1182,7 @@
         <v/>
       </c>
       <c r="G7" s="5" t="str">
-        <f>IF(A7="","",IF(D7=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A7="","",IF(D7=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A7,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A7,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A7,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1179,11 +1191,11 @@
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="9" t="str">
-        <f>IF(A8="","",COUNTIF(Prompts!$B$4:$B$1000,A8))</f>
+        <f>IF(A8="","",COUNTIF(Prompts!$B$4:$B$999,A8))</f>
         <v/>
       </c>
       <c r="E8" s="9" t="str">
-        <f>IF(A8="","",SUMIF(Prompts!$B$4:$B$1000,A8,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A8="","",SUMIF(Prompts!$B$4:$B$999,A8,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F8" s="10" t="str">
@@ -1191,7 +1203,7 @@
         <v/>
       </c>
       <c r="G8" s="5" t="str">
-        <f>IF(A8="","",IF(D8=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A8="","",IF(D8=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A8,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A8,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A8,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1200,11 +1212,11 @@
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="9" t="str">
-        <f>IF(A9="","",COUNTIF(Prompts!$B$4:$B$1000,A9))</f>
+        <f>IF(A9="","",COUNTIF(Prompts!$B$4:$B$999,A9))</f>
         <v/>
       </c>
       <c r="E9" s="9" t="str">
-        <f>IF(A9="","",SUMIF(Prompts!$B$4:$B$1000,A9,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A9="","",SUMIF(Prompts!$B$4:$B$999,A9,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F9" s="10" t="str">
@@ -1212,7 +1224,7 @@
         <v/>
       </c>
       <c r="G9" s="5" t="str">
-        <f>IF(A9="","",IF(D9=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A9="","",IF(D9=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A9,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A9,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A9,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1221,11 +1233,11 @@
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="9" t="str">
-        <f>IF(A10="","",COUNTIF(Prompts!$B$4:$B$1000,A10))</f>
+        <f>IF(A10="","",COUNTIF(Prompts!$B$4:$B$999,A10))</f>
         <v/>
       </c>
       <c r="E10" s="9" t="str">
-        <f>IF(A10="","",SUMIF(Prompts!$B$4:$B$1000,A10,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A10="","",SUMIF(Prompts!$B$4:$B$999,A10,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F10" s="10" t="str">
@@ -1233,7 +1245,7 @@
         <v/>
       </c>
       <c r="G10" s="5" t="str">
-        <f>IF(A10="","",IF(D10=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A10="","",IF(D10=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A10,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A10,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A10,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1242,11 +1254,11 @@
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="9" t="str">
-        <f>IF(A11="","",COUNTIF(Prompts!$B$4:$B$1000,A11))</f>
+        <f>IF(A11="","",COUNTIF(Prompts!$B$4:$B$999,A11))</f>
         <v/>
       </c>
       <c r="E11" s="9" t="str">
-        <f>IF(A11="","",SUMIF(Prompts!$B$4:$B$1000,A11,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A11="","",SUMIF(Prompts!$B$4:$B$999,A11,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F11" s="10" t="str">
@@ -1254,7 +1266,7 @@
         <v/>
       </c>
       <c r="G11" s="5" t="str">
-        <f>IF(A11="","",IF(D11=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A11="","",IF(D11=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A11,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A11,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A11,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1263,11 +1275,11 @@
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="9" t="str">
-        <f>IF(A12="","",COUNTIF(Prompts!$B$4:$B$1000,A12))</f>
+        <f>IF(A12="","",COUNTIF(Prompts!$B$4:$B$999,A12))</f>
         <v/>
       </c>
       <c r="E12" s="9" t="str">
-        <f>IF(A12="","",SUMIF(Prompts!$B$4:$B$1000,A12,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A12="","",SUMIF(Prompts!$B$4:$B$999,A12,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F12" s="10" t="str">
@@ -1275,7 +1287,7 @@
         <v/>
       </c>
       <c r="G12" s="5" t="str">
-        <f>IF(A12="","",IF(D12=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A12="","",IF(D12=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A12,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A12,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A12,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1284,11 +1296,11 @@
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="9" t="str">
-        <f>IF(A13="","",COUNTIF(Prompts!$B$4:$B$1000,A13))</f>
+        <f>IF(A13="","",COUNTIF(Prompts!$B$4:$B$999,A13))</f>
         <v/>
       </c>
       <c r="E13" s="9" t="str">
-        <f>IF(A13="","",SUMIF(Prompts!$B$4:$B$1000,A13,Prompts!$F$4:$F$1000))</f>
+        <f>IF(A13="","",SUMIF(Prompts!$B$4:$B$999,A13,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="F13" s="10" t="str">
@@ -1296,7 +1308,7 @@
         <v/>
       </c>
       <c r="G13" s="5" t="str">
-        <f>IF(A13="","",IF(D13=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A13="","",IF(D13=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A13,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A13,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A13,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1311,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1324,16 +1336,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1641,7 +1653,9 @@
       <c r="E16" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="21" t="s">
+        <v>111</v>
+      </c>
       <c r="G16" s="8"/>
       <c r="H16" s="20" t="s">
         <v>78</v>
@@ -1653,13 +1667,19 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="6"/>
+      <c r="E17" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="G17" s="8"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="20" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="153" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
@@ -1667,7 +1687,7 @@
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="24" t="s">
         <v>107</v>
       </c>
       <c r="E18" s="8"/>
@@ -1677,45 +1697,61 @@
     </row>
     <row r="19" spans="1:8" ht="176.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="6"/>
+      <c r="E19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="G19" s="8"/>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" ht="205.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
+      <c r="H19" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>110</v>
+      </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="6"/>
+      <c r="C20" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="G20" s="8"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" ht="319.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H20" s="20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
-      <c r="C21" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" s="27"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="24"/>
       <c r="E21" s="8"/>
       <c r="F21" s="6"/>
       <c r="G21" s="8"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="1:8" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="27"/>
+      <c r="D22" s="5"/>
       <c r="E22" s="8"/>
       <c r="F22" s="6"/>
       <c r="G22" s="8"/>
@@ -1742,14 +1778,7 @@
       <c r="H24" s="5"/>
     </row>
     <row r="25" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="5"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F26" s="11"/>
@@ -1771,20 +1800,17 @@
     </row>
     <row r="32" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F32" s="11"/>
-    </row>
-    <row r="33" spans="6:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F33" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Pick one of: Draft, Testing, Success, Failed, Needs Review" promptTitle="Status" prompt="Choose a status" sqref="E4:E1000" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Pick one of: Draft, Testing, Success, Failed, Needs Review" promptTitle="Status" prompt="Choose a status" sqref="E4:E999" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Draft,Testing,Success,Failed,Needs Review"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" errorTitle="Invalid tokens" error="Tokens must be a whole number ≥ 0" sqref="F4:F1000" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" errorTitle="Invalid tokens" error="Tokens must be a whole number ≥ 0" sqref="F4:F999" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1802,7 +1828,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>B4:B1000</xm:sqref>
+          <xm:sqref>B4:B999</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1826,19 +1852,19 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B4" s="13">
-        <f>COUNTA(Prompts!A4:A1000)</f>
-        <v>16</v>
+        <f>COUNTA(Prompts!A4:A999)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1855,7 +1881,7 @@
         <v>57</v>
       </c>
       <c r="B6" s="13">
-        <f>SUM(Prompts!F4:F1000)</f>
+        <f>SUM(Prompts!F4:F999)</f>
         <v>0</v>
       </c>
     </row>
@@ -1864,7 +1890,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="13">
-        <f>IFERROR(SUM(Prompts!F4:F1000)/COUNTIF(Prompts!F4:F1000,"&gt;0"),0)</f>
+        <f>IFERROR(SUM(Prompts!F4:F999)/COUNTIF(Prompts!F4:F999,"&gt;0"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1873,7 +1899,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="13">
-        <f>IFERROR(MAX(Prompts!F4:F1000),0)</f>
+        <f>IFERROR(MAX(Prompts!F4:F999),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1882,7 +1908,7 @@
         <v>60</v>
       </c>
       <c r="B9" s="13">
-        <f>IFERROR(SMALL(Prompts!F4:F1000,COUNTIF(Prompts!F4:F1000,0)+1),0)</f>
+        <f>IFERROR(SMALL(Prompts!F4:F999,COUNTIF(Prompts!F4:F999,0)+1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1891,8 +1917,8 @@
         <v>61</v>
       </c>
       <c r="B10" s="14">
-        <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Success")/COUNTA(Prompts!A4:A1000),0)</f>
-        <v>0.5625</v>
+        <f>IFERROR(COUNTIF(Prompts!E4:E999,"Success")/COUNTA(Prompts!A4:A999),0)</f>
+        <v>0.70588235294117652</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1900,16 +1926,16 @@
         <v>62</v>
       </c>
       <c r="B11" s="14">
-        <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Failed")/COUNTA(Prompts!A4:A1000),0)</f>
-        <v>0.1875</v>
+        <f>IFERROR(COUNTIF(Prompts!E4:E999,"Failed")/COUNTA(Prompts!A4:A999),0)</f>
+        <v>0.17647058823529413</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
+      <c r="A14" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
@@ -1927,11 +1953,11 @@
         <v>46</v>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(Prompts!E4:E1000,A16)</f>
+        <f>COUNTIF(Prompts!E4:E999,A16)</f>
         <v>0</v>
       </c>
       <c r="C16" s="15">
-        <f>SUMIF(Prompts!E4:E1000,A16,Prompts!F4:F1000)</f>
+        <f>SUMIF(Prompts!E4:E999,A16,Prompts!F4:F999)</f>
         <v>0</v>
       </c>
     </row>
@@ -1940,11 +1966,11 @@
         <v>44</v>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(Prompts!E4:E1000,A17)</f>
+        <f>COUNTIF(Prompts!E4:E999,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="15">
-        <f>SUMIF(Prompts!E4:E1000,A17,Prompts!F4:F1000)</f>
+        <f>SUMIF(Prompts!E4:E999,A17,Prompts!F4:F999)</f>
         <v>0</v>
       </c>
     </row>
@@ -1953,11 +1979,11 @@
         <v>42</v>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF(Prompts!E4:E1000,A18)</f>
-        <v>9</v>
+        <f>COUNTIF(Prompts!E4:E999,A18)</f>
+        <v>12</v>
       </c>
       <c r="C18" s="15">
-        <f>SUMIF(Prompts!E4:E1000,A18,Prompts!F4:F1000)</f>
+        <f>SUMIF(Prompts!E4:E999,A18,Prompts!F4:F999)</f>
         <v>0</v>
       </c>
     </row>
@@ -1966,11 +1992,11 @@
         <v>52</v>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF(Prompts!E4:E1000,A19)</f>
+        <f>COUNTIF(Prompts!E4:E999,A19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="15">
-        <f>SUMIF(Prompts!E4:E1000,A19,Prompts!F4:F1000)</f>
+        <f>SUMIF(Prompts!E4:E999,A19,Prompts!F4:F999)</f>
         <v>0</v>
       </c>
     </row>
@@ -1979,11 +2005,11 @@
         <v>49</v>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF(Prompts!E4:E1000,A20)</f>
+        <f>COUNTIF(Prompts!E4:E999,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="15">
-        <f>SUMIF(Prompts!E4:E1000,A20,Prompts!F4:F1000)</f>
+        <f>SUMIF(Prompts!E4:E999,A20,Prompts!F4:F999)</f>
         <v>0</v>
       </c>
     </row>
@@ -1993,7 +2019,7 @@
       </c>
       <c r="B21" s="17">
         <f>SUM(B16:B20)</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C21" s="17">
         <f>SUM(C16:C20)</f>
@@ -2001,14 +2027,14 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
     </row>
     <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
@@ -2040,15 +2066,15 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <f>IF(Groups!A4="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A4))</f>
+        <f>IF(Groups!A4="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A4))</f>
         <v>3</v>
       </c>
       <c r="D26" s="15">
-        <f>IF(Groups!A4="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A4="","",SUMIF(Prompts!$B$4:$B$999,Groups!A4,Prompts!$F$4:$F$999))</f>
         <v>0</v>
       </c>
       <c r="E26" s="15">
-        <f>IF(Groups!A4="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A4="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A4,Prompts!$E$4:$E$999,"Success"))</f>
         <v>3</v>
       </c>
       <c r="F26" s="18">
@@ -2066,15 +2092,15 @@
         <v>0</v>
       </c>
       <c r="C27" s="15">
-        <f>IF(Groups!A5="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A5))</f>
+        <f>IF(Groups!A5="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A5))</f>
         <v>3</v>
       </c>
       <c r="D27" s="15">
-        <f>IF(Groups!A5="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A5="","",SUMIF(Prompts!$B$4:$B$999,Groups!A5,Prompts!$F$4:$F$999))</f>
         <v>0</v>
       </c>
       <c r="E27" s="15">
-        <f>IF(Groups!A5="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A5="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A5,Prompts!$E$4:$E$999,"Success"))</f>
         <v>2</v>
       </c>
       <c r="F27" s="18">
@@ -2092,15 +2118,15 @@
         <v/>
       </c>
       <c r="C28" s="15" t="str">
-        <f>IF(Groups!A6="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A6))</f>
+        <f>IF(Groups!A6="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A6))</f>
         <v/>
       </c>
       <c r="D28" s="15" t="str">
-        <f>IF(Groups!A6="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A6="","",SUMIF(Prompts!$B$4:$B$999,Groups!A6,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E28" s="15" t="str">
-        <f>IF(Groups!A6="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A6="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A6,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F28" s="18" t="str">
@@ -2118,15 +2144,15 @@
         <v/>
       </c>
       <c r="C29" s="15" t="str">
-        <f>IF(Groups!A7="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A7))</f>
+        <f>IF(Groups!A7="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A7))</f>
         <v/>
       </c>
       <c r="D29" s="15" t="str">
-        <f>IF(Groups!A7="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A7="","",SUMIF(Prompts!$B$4:$B$999,Groups!A7,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E29" s="15" t="str">
-        <f>IF(Groups!A7="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A7="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A7,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F29" s="18" t="str">
@@ -2144,15 +2170,15 @@
         <v/>
       </c>
       <c r="C30" s="15" t="str">
-        <f>IF(Groups!A8="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A8))</f>
+        <f>IF(Groups!A8="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A8))</f>
         <v/>
       </c>
       <c r="D30" s="15" t="str">
-        <f>IF(Groups!A8="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A8="","",SUMIF(Prompts!$B$4:$B$999,Groups!A8,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E30" s="15" t="str">
-        <f>IF(Groups!A8="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A8="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A8,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F30" s="18" t="str">
@@ -2170,15 +2196,15 @@
         <v/>
       </c>
       <c r="C31" s="15" t="str">
-        <f>IF(Groups!A9="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A9))</f>
+        <f>IF(Groups!A9="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A9))</f>
         <v/>
       </c>
       <c r="D31" s="15" t="str">
-        <f>IF(Groups!A9="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A9="","",SUMIF(Prompts!$B$4:$B$999,Groups!A9,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E31" s="15" t="str">
-        <f>IF(Groups!A9="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A9="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A9,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F31" s="18" t="str">
@@ -2196,15 +2222,15 @@
         <v/>
       </c>
       <c r="C32" s="15" t="str">
-        <f>IF(Groups!A10="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A10))</f>
+        <f>IF(Groups!A10="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A10))</f>
         <v/>
       </c>
       <c r="D32" s="15" t="str">
-        <f>IF(Groups!A10="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A10="","",SUMIF(Prompts!$B$4:$B$999,Groups!A10,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E32" s="15" t="str">
-        <f>IF(Groups!A10="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A10="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A10,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F32" s="18" t="str">
@@ -2222,15 +2248,15 @@
         <v/>
       </c>
       <c r="C33" s="15" t="str">
-        <f>IF(Groups!A11="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A11))</f>
+        <f>IF(Groups!A11="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A11))</f>
         <v/>
       </c>
       <c r="D33" s="15" t="str">
-        <f>IF(Groups!A11="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A11="","",SUMIF(Prompts!$B$4:$B$999,Groups!A11,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E33" s="15" t="str">
-        <f>IF(Groups!A11="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A11="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A11,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F33" s="18" t="str">
@@ -2248,15 +2274,15 @@
         <v/>
       </c>
       <c r="C34" s="15" t="str">
-        <f>IF(Groups!A12="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A12))</f>
+        <f>IF(Groups!A12="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A12))</f>
         <v/>
       </c>
       <c r="D34" s="15" t="str">
-        <f>IF(Groups!A12="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A12="","",SUMIF(Prompts!$B$4:$B$999,Groups!A12,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E34" s="15" t="str">
-        <f>IF(Groups!A12="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A12="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A12,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F34" s="18" t="str">
@@ -2274,15 +2300,15 @@
         <v/>
       </c>
       <c r="C35" s="15" t="str">
-        <f>IF(Groups!A13="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A13))</f>
+        <f>IF(Groups!A13="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A13))</f>
         <v/>
       </c>
       <c r="D35" s="15" t="str">
-        <f>IF(Groups!A13="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$F$4:$F$1000))</f>
+        <f>IF(Groups!A13="","",SUMIF(Prompts!$B$4:$B$999,Groups!A13,Prompts!$F$4:$F$999))</f>
         <v/>
       </c>
       <c r="E35" s="15" t="str">
-        <f>IF(Groups!A13="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$E$4:$E$1000,"Success"))</f>
+        <f>IF(Groups!A13="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A13,Prompts!$E$4:$E$999,"Success"))</f>
         <v/>
       </c>
       <c r="F35" s="18" t="str">

--- a/jira_clone/prompt_study.xlsx
+++ b/jira_clone/prompt_study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB665309-45F8-4764-8F89-40C38579A15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57529FF3-DC37-4376-8F79-C6011EB582D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="131">
   <si>
     <t>Prompt Study Workbook</t>
   </si>
@@ -470,6 +470,232 @@
   </si>
   <si>
     <t>task 19</t>
+  </si>
+  <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>&gt; please eliminate the unecessary element tag that put just for design in all lwc component just igonore the `@force-app/main/default/classes/controller/manageTicketTracking/`, `@force-app/main/default/classes/controller/manageWorkflow/`, `@force-app/main/default/lwc/manageWorkflowForm/`, `@force-app/main/default/lwc/projectMember/`, `@force-app/main/default/lwc/projectSelector/`, `@force-app/main/default/lwc/workflowVisualizer/`.
+&gt;
+&gt; use a modern style that looks like jira:
+&gt;
+&gt; **Jira-Like Frontend Design Plan**
+&gt;
+&gt; **Visual Identity &amp; Design System**
+&gt;
+&gt; **Color Palette**
+&gt; - Background: `#1D2125` (dark nav), `#FFFFFF` (main content), `#F4F5F7` (sidebar/panel bg)
+&gt; - Primary Blue: `#0052CC` (buttons, links, active states)
+&gt; - Accent: `#0065FF` (hover states)
+&gt; - Text: `#172B4D` (primary), `#6B778C` (secondary/muted)
+&gt; - Borders: `#DFE1E6`
+&gt; - Status chips: green `#00875A`, orange `#FF991F`, red `#DE350B`, purple `#6554C0`
+&gt;
+&gt; **Typography**
+&gt; - Font: `-apple-system, BlinkMacSystemFont, "Segoe UI"` — Jira uses system fonts for speed and neutrality
+&gt; - Base size: 14px, line-height 1.4
+&gt; - Headings: 20–24px, weight 600
+&gt;
+&gt; **Layout Structure**
+&gt; ```
+&gt; ┌──────────────────────────────────────────────────────┐
+&gt; │  TOP NAV (56px)  — Logo | Projects | Boards | Search │
+&gt; ├──────┬───────────────────────────────────────────────┤
+&gt; │      │  BREADCRUMB BAR                               │
+&gt; │ SIDE │───────────────────────────────────────────────┤
+&gt; │ BAR  │                                               │
+&gt; │(64px │         MAIN CONTENT AREA                     │
+&gt; │ col- │         (Board / Backlog / Issue Detail)       │
+&gt; │ laps)│                                               │
+&gt; │      │                                               │
+&gt; └──────┴───────────────────────────────────────────────┘
+&gt; ```
+&gt;
+&gt; **Core Components to Build**
+&gt;
+&gt; 1. **Top Navigation Bar** — Logo + product switcher icon, breadcrumb (`Projects &gt; My Project &gt; Board`), global search (`/` shortcut trigger), Create button (blue, pill shape), Avatar + notifications icon (right side).
+&gt; 2. **Left Sidebar** — Icon-based collapsed nav (64px wide), expandable to 240px with labels. Sections: Board, Backlog, Reports, Project Settings. Active state: blue left border + blue icon.
+&gt; 3. **Kanban Board** — Horizontal scrollable columns; column header: name + issue count badge; cards with issue key (`PROJ-123`), title, assignee avatar, priority icon, story points; drag-and-drop between columns (use a library like dnd-kit); column footer: "+ Create issue" link.
+&gt; 4. **Issue Card** — Priority icon (↑ high, = medium, ↓ low), issue type icon (bug 🐛, story 📖, task ✓), truncated title, bottom row: issue key (muted), assignee avatar (right-aligned). Hover: slight elevation shadow.
+&gt; 5. **Issue Detail Panel / Modal** — Slide-in right panel (50% width) OR full modal. Left: title (editable inline), description (rich text), comments. Right sidebar: status dropdown, assignee, reporter, priority, sprint, story points, labels. Status: pill dropdown with color-coded options.
+&gt; 6. **Backlog View** — Grouped list by sprint (collapsible sections). Each row: drag handle, issue type icon, key, title, assignee, story points, priority. Sprint header: name, dates, start/complete sprint button.
+&gt; 7. **Status Dropdown (pill-style)** — Rounded badge buttons: TO DO (gray), IN PROGRESS (blue), DONE (green). Click to cycle or open mini-dropdown.
+&gt;
+&gt; **Component States to Handle**
+&gt;
+&gt; | Component       | States                                               |
+&gt; | --------------- | ---------------------------------------------------- |
+&gt; | Buttons         | Default, Hover, Active, Disabled, Loading            |
+&gt; | Cards           | Default, Hover, Dragging, Selected                   |
+&gt; | Inputs          | Default, Focus, Error, Disabled                      |
+&gt; | Sidebar items   | Default, Hover, Active                               |
+&gt; | Dropdowns       | Closed, Open, Selected                               |
+&gt;
+&gt; **Recommended Tech Stack**
+&gt;
+&gt; | Layer         | Choice                                              |
+&gt; | ------------- | --------------------------------------------------- |
+&gt; | Framework     | React (JSX)                                         |
+&gt; | Styling       | Tailwind CSS utility classes OR CSS Modules         |
+&gt; | Icons         | `lucide-react` or Atlassian's icon set              |
+&gt; | Drag &amp; Drop   | `@dnd-kit/core`                                     |
+&gt; | Rich Text     | `@tiptap/react` (for descriptions)                  |
+&gt; | State         | `useState` + `useReducer` (or Zustand for scale)    |
+&gt; | Routing       | React Router (Board / Backlog / Settings routes)    |
+&gt;
+&gt; so all the update related to html unecessary div and css
+---</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>Claude Opus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what i need from you 
+TASK1 : is to delete the _updateSprint method in  @force-app/main/default/lwc/manageBacklog/manageBacklog.js  and create a method _enrichSprintWith&lt;&gt; based on the call so we will have for each action that enrich sprint a new function . 
+ TASK 2 : DO THE SAME FOR THE _updateTicketInSprints in  @force-app/main/default/lwc/manageBacklog/manageBacklog.js  </t>
+  </si>
+  <si>
+    <t>task 23</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>task 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in @force-app/main/default/classes/controller/managebacklog/    we have call deleteTicket and deleteTickets where the response is change now we return in deleteTicket          :
+            Map&lt;String, Object&gt; data = new Map&lt;String, Object&gt;{
+                'updatedSprint' =&gt; updatedSprint
+            };
+            return new APIResponse(true, 'Ticket deleted', data);
+so  after call them in .then in _enrichSprintsWithoutTicket update the totalStoryPoint based on the return response so we need to set the new value that came  from the server sprint.totalStoryPoint after format the returned Sprint 
+</t>
+  </si>
+  <si>
+    <t>`do the same for _executeBulkDelete in @force-app/main/default/lwc/manageBacklog/manageBacklog.js  when the deleteTickets return  
+            Map&lt;String, Object&gt; data = new Map&lt;String, Object&gt;{
+                'updatedSprints' =&gt; updatedSprints
+            };
+            return new APIResponse(true, 'Tickets deleted', data);
+also create a enrich SprintsWithoutTickets for it that also update the totalStoryPoints for each sprint and also spread it without the deleted tickets</t>
+  </si>
+  <si>
+    <t>Claude haiku</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>excellent but more clariffy for formatSprint</t>
+  </si>
+  <si>
+    <t>`in @force-app/main/default/classes/domain/TicketService.cls  update the : 
+    // Todo return the Sprint object 
+    public static void deleteTicket(Ticket__c ticket) {
+        try {
+            ticket.RecordStatus__c = 'delete';
+            updateTicket(ticket);
+            //Todo SprintService.decreaseTotalStoryPoint(ticket.Sprint__c, ticket.TotalStoryPoint__c);&gt;&gt; return full sprint object 
+        } catch (DmlException dex) {
+            throw new ServiceException('DML error deleting ticket: ' + dex.getMessage());
+        } catch (Exception ex) {
+            throw new ServiceException('Error deleting ticket: ' + ex.getMessage());
+        }
+    }
+    // Todo pass the sprintId also as input 
+    // Todo pass List of Ticket instead of list of ticket Id 
+    // return the array of sprint 
+    public static void deleteTickets(List&lt;String&gt; ticketIds) {
+        try {
+            List&lt;Ticket__c&gt; found = [SELECT Id, RecordStatus__c, Ticket_Type__c, Description__c, Creator__c FROM Ticket__c WHERE Id IN :ticketIds];
+            if (!found.isEmpty()) {
+                for (Ticket__c t : found) t.RecordStatus__c = 'delete';
+                update found;
+            }
+            //Todo  SprintService.decreaseTotalStoryPoint(); with passing the sprintId and the totalStory point to decreased 
+        } catch (DmlException dex) {
+            throw new ServiceException('DML error deleting tickets: ' + dex.getMessage());
+        } catch (Exception ex) {
+            throw new ServiceException('Error deleting tickets: ' + ex.getMessage());
+        }
+    }
+and create the necessary  method in @force-app/main/default/classes/domain/SprintService.cls  decreaseTotalStoryPoint. 
+Then update in @force-app/main/default/classes/controller/managebacklog/ManageBacklogController.cls  the :   
+    @AuraEnabled
+    public static APIResponse deleteTicket(String ticketId) {
+        try {
+            if (String.isBlank(ticketId)) return new APIResponse(false, 'ticketId is required');
+            Ticket__c existing = DomainCorrectness.requireTicketExists(ticketId);
+            TicketService.deleteTicket(existing);
+            // Todo return in the data the updated sprint 
+            return new APIResponse(true, 'Ticket deleted');
+        } catch (Exception ex) {
+            return new APIResponse(false, 'Error deleting ticket: ' + ex.getMessage());
+        }
+    }
+    @AuraEnabled
+    public static APIResponse deleteTickets(List&lt;String&gt; ticketIds) {
+        try {
+            if (ticketIds == null || ticketIds.isEmpty()) return new APIResponse(false, 'ticketIds are required');
+            // Todo do DomainCorrectness for all tickets  and pass the List of Ticket__c instead of String
+            TicketService.deleteTickets(ticketIds);
+            // Todo return the updated sprints
+            return new APIResponse(true, 'Tickets deleted');
+        } catch (Exception ex) {
+            return new APIResponse(false, 'Error deleting tickets: ' + ex.getMessage());
+        }
+    }
+Then update the frontEnd call in @force-app/main/default/lwc/manageBacklog/manageBacklog.js where we should update the sprint.totalStoryPoint based on this call in :   handleTicketDelete(event) {
+        const { ticketId } = event.detail;
+        const ticketItem   = event.target;
+        deleteTicket({ ticketId })
+            .then(res =&gt; {
+                this.isLoading = true;
+                if (!res.success) { ticketItem.ticketError = res.message; return; }
+                this.backlogTickets = this.backlogTickets.filter(t =&gt; t.Id !== ticketId);
+                this._selectedTicketIds.delete(ticketId);
+                this._selectedTicketIds = new Set(this._selectedTicketIds);
+                this._enrichSprintsWithoutTicket(ticketId);
+// Todo updateSprintTotalStoryPoint 
+                this._showSuccess('Ticket deleted');
+            })
+            .catch(err =&gt; { ticketItem.ticketError = err.body?.message || 'Error deleting ticket'; })
+            .finally(() =&gt; { this.isLoading = false; });
+    }
+_executeBulkDelete() {
+        const ids = [...this._selectedTicketIds];
+        deleteTickets({ ticketIds: ids })
+            .then(res =&gt; {
+                this.isLoading = true;
+                if (!res.success) { this.errorMessage = res.message; return; }
+                this.backlogTickets     = this.backlogTickets.filter(t =&gt; !ids.includes(t.Id));
+                this._selectedTicketIds = new Set();
+                this.sprints = [...this.sprints.map(s =&gt; {
+                    const tickets = s.tickets.filter(t =&gt; !ids.includes(t.Id));
+                    return { ...s, tickets, hasTickets: tickets.length &gt; 0 };
+                })];
+                this._showSuccess('Tickets deleted');
+                // Todo update the sprints total story point 
+            })
+            .catch(err =&gt; { this.errorMessage = err.body?.message || 'Error deleting tickets'; })
+            .finally(() =&gt; { this.isLoading = false; });
+        }</t>
+  </si>
+  <si>
+    <t>P020</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>Task 30</t>
   </si>
 </sst>
 </file>
@@ -1127,11 +1353,11 @@
         <v>70</v>
       </c>
       <c r="D4" s="6">
-        <f>COUNTIF(Prompts!$B$4:$B$999,A4)</f>
+        <f>COUNTIF(Prompts!$B$4:$B$1000,A4)</f>
         <v>3</v>
       </c>
       <c r="E4" s="6">
-        <f>SUMIF(Prompts!$B$4:$B$999,A4,Prompts!$F$4:$F$999)</f>
+        <f>SUMIF(Prompts!$B$4:$B$1000,A4,Prompts!$F$4:$F$1000)</f>
         <v>0</v>
       </c>
       <c r="F4" s="7">
@@ -1139,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="8" t="str">
-        <f>IF(D4=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A4,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A4,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A4,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress"))</f>
+        <f>IF(D4=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A4,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress"))</f>
         <v>Complete</v>
       </c>
     </row>
@@ -1170,11 +1396,11 @@
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
       <c r="D7" s="9" t="str">
-        <f>IF(A7="","",COUNTIF(Prompts!$B$4:$B$999,A7))</f>
+        <f>IF(A7="","",COUNTIF(Prompts!$B$4:$B$1000,A7))</f>
         <v/>
       </c>
       <c r="E7" s="9" t="str">
-        <f>IF(A7="","",SUMIF(Prompts!$B$4:$B$999,A7,Prompts!$F$4:$F$999))</f>
+        <f>IF(A7="","",SUMIF(Prompts!$B$4:$B$1000,A7,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F7" s="10" t="str">
@@ -1182,7 +1408,7 @@
         <v/>
       </c>
       <c r="G7" s="5" t="str">
-        <f>IF(A7="","",IF(D7=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A7,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A7,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A7,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A7="","",IF(D7=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A7,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1191,11 +1417,11 @@
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="9" t="str">
-        <f>IF(A8="","",COUNTIF(Prompts!$B$4:$B$999,A8))</f>
+        <f>IF(A8="","",COUNTIF(Prompts!$B$4:$B$1000,A8))</f>
         <v/>
       </c>
       <c r="E8" s="9" t="str">
-        <f>IF(A8="","",SUMIF(Prompts!$B$4:$B$999,A8,Prompts!$F$4:$F$999))</f>
+        <f>IF(A8="","",SUMIF(Prompts!$B$4:$B$1000,A8,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F8" s="10" t="str">
@@ -1203,7 +1429,7 @@
         <v/>
       </c>
       <c r="G8" s="5" t="str">
-        <f>IF(A8="","",IF(D8=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A8,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A8,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A8,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A8="","",IF(D8=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A8,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1212,11 +1438,11 @@
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
       <c r="D9" s="9" t="str">
-        <f>IF(A9="","",COUNTIF(Prompts!$B$4:$B$999,A9))</f>
+        <f>IF(A9="","",COUNTIF(Prompts!$B$4:$B$1000,A9))</f>
         <v/>
       </c>
       <c r="E9" s="9" t="str">
-        <f>IF(A9="","",SUMIF(Prompts!$B$4:$B$999,A9,Prompts!$F$4:$F$999))</f>
+        <f>IF(A9="","",SUMIF(Prompts!$B$4:$B$1000,A9,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F9" s="10" t="str">
@@ -1224,7 +1450,7 @@
         <v/>
       </c>
       <c r="G9" s="5" t="str">
-        <f>IF(A9="","",IF(D9=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A9,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A9,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A9,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A9="","",IF(D9=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A9,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1233,11 +1459,11 @@
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
       <c r="D10" s="9" t="str">
-        <f>IF(A10="","",COUNTIF(Prompts!$B$4:$B$999,A10))</f>
+        <f>IF(A10="","",COUNTIF(Prompts!$B$4:$B$1000,A10))</f>
         <v/>
       </c>
       <c r="E10" s="9" t="str">
-        <f>IF(A10="","",SUMIF(Prompts!$B$4:$B$999,A10,Prompts!$F$4:$F$999))</f>
+        <f>IF(A10="","",SUMIF(Prompts!$B$4:$B$1000,A10,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F10" s="10" t="str">
@@ -1245,7 +1471,7 @@
         <v/>
       </c>
       <c r="G10" s="5" t="str">
-        <f>IF(A10="","",IF(D10=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A10,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A10,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A10,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A10="","",IF(D10=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A10,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1254,11 +1480,11 @@
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="9" t="str">
-        <f>IF(A11="","",COUNTIF(Prompts!$B$4:$B$999,A11))</f>
+        <f>IF(A11="","",COUNTIF(Prompts!$B$4:$B$1000,A11))</f>
         <v/>
       </c>
       <c r="E11" s="9" t="str">
-        <f>IF(A11="","",SUMIF(Prompts!$B$4:$B$999,A11,Prompts!$F$4:$F$999))</f>
+        <f>IF(A11="","",SUMIF(Prompts!$B$4:$B$1000,A11,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F11" s="10" t="str">
@@ -1266,7 +1492,7 @@
         <v/>
       </c>
       <c r="G11" s="5" t="str">
-        <f>IF(A11="","",IF(D11=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A11,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A11,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A11,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A11="","",IF(D11=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A11,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1275,11 +1501,11 @@
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="9" t="str">
-        <f>IF(A12="","",COUNTIF(Prompts!$B$4:$B$999,A12))</f>
+        <f>IF(A12="","",COUNTIF(Prompts!$B$4:$B$1000,A12))</f>
         <v/>
       </c>
       <c r="E12" s="9" t="str">
-        <f>IF(A12="","",SUMIF(Prompts!$B$4:$B$999,A12,Prompts!$F$4:$F$999))</f>
+        <f>IF(A12="","",SUMIF(Prompts!$B$4:$B$1000,A12,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F12" s="10" t="str">
@@ -1287,7 +1513,7 @@
         <v/>
       </c>
       <c r="G12" s="5" t="str">
-        <f>IF(A12="","",IF(D12=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A12,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A12,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A12,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A12="","",IF(D12=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A12,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1296,11 +1522,11 @@
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="9" t="str">
-        <f>IF(A13="","",COUNTIF(Prompts!$B$4:$B$999,A13))</f>
+        <f>IF(A13="","",COUNTIF(Prompts!$B$4:$B$1000,A13))</f>
         <v/>
       </c>
       <c r="E13" s="9" t="str">
-        <f>IF(A13="","",SUMIF(Prompts!$B$4:$B$999,A13,Prompts!$F$4:$F$999))</f>
+        <f>IF(A13="","",SUMIF(Prompts!$B$4:$B$1000,A13,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="F13" s="10" t="str">
@@ -1308,7 +1534,7 @@
         <v/>
       </c>
       <c r="G13" s="5" t="str">
-        <f>IF(A13="","",IF(D13=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$999,A13,Prompts!$E$4:$E$999,"Draft")+COUNTIFS(Prompts!$B$4:$B$999,A13,Prompts!$E$4:$E$999,"Testing")+COUNTIFS(Prompts!$B$4:$B$999,A13,Prompts!$E$4:$E$999,"Needs Review")=0,"Complete","In Progress")))</f>
+        <f>IF(A13="","",IF(D13=0,"Empty",IF(COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Draft")+COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Testing")+COUNTIFS(Prompts!$B$4:$B$1000,A13,Prompts!$E$4:$E$1000,"Needs Review")=0,"Complete","In Progress")))</f>
         <v/>
       </c>
     </row>
@@ -1323,7 +1549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1737,48 +1963,125 @@
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
+    <row r="21" spans="1:8" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
+      <c r="A22" s="8" t="s">
+        <v>119</v>
+      </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="5"/>
+      <c r="C22" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
+      <c r="A23" s="19" t="s">
+        <v>127</v>
+      </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="5"/>
+      <c r="C23" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="19" t="s">
+        <v>128</v>
+      </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="5"/>
+      <c r="C24" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F25" s="11"/>
+      <c r="A25" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F26" s="11"/>
@@ -1800,17 +2103,20 @@
     </row>
     <row r="32" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="6:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F33" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Pick one of: Draft, Testing, Success, Failed, Needs Review" promptTitle="Status" prompt="Choose a status" sqref="E4:E999" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid status" error="Pick one of: Draft, Testing, Success, Failed, Needs Review" promptTitle="Status" prompt="Choose a status" sqref="E4:E1000" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Draft,Testing,Success,Failed,Needs Review"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" errorTitle="Invalid tokens" error="Tokens must be a whole number ≥ 0" sqref="F4:F999" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" errorTitle="Invalid tokens" error="Tokens must be a whole number ≥ 0" sqref="F4:F1000" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1828,7 +2134,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>B4:B999</xm:sqref>
+          <xm:sqref>B4:B1000</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1863,8 +2169,8 @@
         <v>55</v>
       </c>
       <c r="B4" s="13">
-        <f>COUNTA(Prompts!A4:A999)</f>
-        <v>17</v>
+        <f>COUNTA(Prompts!A4:A1000)</f>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1881,7 +2187,7 @@
         <v>57</v>
       </c>
       <c r="B6" s="13">
-        <f>SUM(Prompts!F4:F999)</f>
+        <f>SUM(Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
@@ -1890,7 +2196,7 @@
         <v>58</v>
       </c>
       <c r="B7" s="13">
-        <f>IFERROR(SUM(Prompts!F4:F999)/COUNTIF(Prompts!F4:F999,"&gt;0"),0)</f>
+        <f>IFERROR(SUM(Prompts!F4:F1000)/COUNTIF(Prompts!F4:F1000,"&gt;0"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1899,7 +2205,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="13">
-        <f>IFERROR(MAX(Prompts!F4:F999),0)</f>
+        <f>IFERROR(MAX(Prompts!F4:F1000),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1908,7 +2214,7 @@
         <v>60</v>
       </c>
       <c r="B9" s="13">
-        <f>IFERROR(SMALL(Prompts!F4:F999,COUNTIF(Prompts!F4:F999,0)+1),0)</f>
+        <f>IFERROR(SMALL(Prompts!F4:F1000,COUNTIF(Prompts!F4:F1000,0)+1),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -1917,8 +2223,8 @@
         <v>61</v>
       </c>
       <c r="B10" s="14">
-        <f>IFERROR(COUNTIF(Prompts!E4:E999,"Success")/COUNTA(Prompts!A4:A999),0)</f>
-        <v>0.70588235294117652</v>
+        <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Success")/COUNTA(Prompts!A4:A1000),0)</f>
+        <v>0.77272727272727271</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -1926,8 +2232,8 @@
         <v>62</v>
       </c>
       <c r="B11" s="14">
-        <f>IFERROR(COUNTIF(Prompts!E4:E999,"Failed")/COUNTA(Prompts!A4:A999),0)</f>
-        <v>0.17647058823529413</v>
+        <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Failed")/COUNTA(Prompts!A4:A1000),0)</f>
+        <v>0.13636363636363635</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -1953,11 +2259,11 @@
         <v>46</v>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(Prompts!E4:E999,A16)</f>
+        <f>COUNTIF(Prompts!E4:E1000,A16)</f>
         <v>0</v>
       </c>
       <c r="C16" s="15">
-        <f>SUMIF(Prompts!E4:E999,A16,Prompts!F4:F999)</f>
+        <f>SUMIF(Prompts!E4:E1000,A16,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
@@ -1966,11 +2272,11 @@
         <v>44</v>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(Prompts!E4:E999,A17)</f>
+        <f>COUNTIF(Prompts!E4:E1000,A17)</f>
         <v>0</v>
       </c>
       <c r="C17" s="15">
-        <f>SUMIF(Prompts!E4:E999,A17,Prompts!F4:F999)</f>
+        <f>SUMIF(Prompts!E4:E1000,A17,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
@@ -1979,11 +2285,11 @@
         <v>42</v>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF(Prompts!E4:E999,A18)</f>
-        <v>12</v>
+        <f>COUNTIF(Prompts!E4:E1000,A18)</f>
+        <v>17</v>
       </c>
       <c r="C18" s="15">
-        <f>SUMIF(Prompts!E4:E999,A18,Prompts!F4:F999)</f>
+        <f>SUMIF(Prompts!E4:E1000,A18,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
@@ -1992,11 +2298,11 @@
         <v>52</v>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF(Prompts!E4:E999,A19)</f>
+        <f>COUNTIF(Prompts!E4:E1000,A19)</f>
         <v>3</v>
       </c>
       <c r="C19" s="15">
-        <f>SUMIF(Prompts!E4:E999,A19,Prompts!F4:F999)</f>
+        <f>SUMIF(Prompts!E4:E1000,A19,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
@@ -2005,11 +2311,11 @@
         <v>49</v>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF(Prompts!E4:E999,A20)</f>
+        <f>COUNTIF(Prompts!E4:E1000,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="15">
-        <f>SUMIF(Prompts!E4:E999,A20,Prompts!F4:F999)</f>
+        <f>SUMIF(Prompts!E4:E1000,A20,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
@@ -2019,7 +2325,7 @@
       </c>
       <c r="B21" s="17">
         <f>SUM(B16:B20)</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C21" s="17">
         <f>SUM(C16:C20)</f>
@@ -2066,15 +2372,15 @@
         <v>0</v>
       </c>
       <c r="C26" s="15">
-        <f>IF(Groups!A4="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A4))</f>
+        <f>IF(Groups!A4="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A4))</f>
         <v>3</v>
       </c>
       <c r="D26" s="15">
-        <f>IF(Groups!A4="","",SUMIF(Prompts!$B$4:$B$999,Groups!A4,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A4="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$F$4:$F$1000))</f>
         <v>0</v>
       </c>
       <c r="E26" s="15">
-        <f>IF(Groups!A4="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A4,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A4="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$E$4:$E$1000,"Success"))</f>
         <v>3</v>
       </c>
       <c r="F26" s="18">
@@ -2092,15 +2398,15 @@
         <v>0</v>
       </c>
       <c r="C27" s="15">
-        <f>IF(Groups!A5="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A5))</f>
+        <f>IF(Groups!A5="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A5))</f>
         <v>3</v>
       </c>
       <c r="D27" s="15">
-        <f>IF(Groups!A5="","",SUMIF(Prompts!$B$4:$B$999,Groups!A5,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A5="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$F$4:$F$1000))</f>
         <v>0</v>
       </c>
       <c r="E27" s="15">
-        <f>IF(Groups!A5="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A5,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A5="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$E$4:$E$1000,"Success"))</f>
         <v>2</v>
       </c>
       <c r="F27" s="18">
@@ -2118,15 +2424,15 @@
         <v/>
       </c>
       <c r="C28" s="15" t="str">
-        <f>IF(Groups!A6="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A6))</f>
+        <f>IF(Groups!A6="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A6))</f>
         <v/>
       </c>
       <c r="D28" s="15" t="str">
-        <f>IF(Groups!A6="","",SUMIF(Prompts!$B$4:$B$999,Groups!A6,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A6="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E28" s="15" t="str">
-        <f>IF(Groups!A6="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A6,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A6="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F28" s="18" t="str">
@@ -2144,15 +2450,15 @@
         <v/>
       </c>
       <c r="C29" s="15" t="str">
-        <f>IF(Groups!A7="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A7))</f>
+        <f>IF(Groups!A7="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A7))</f>
         <v/>
       </c>
       <c r="D29" s="15" t="str">
-        <f>IF(Groups!A7="","",SUMIF(Prompts!$B$4:$B$999,Groups!A7,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A7="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E29" s="15" t="str">
-        <f>IF(Groups!A7="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A7,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A7="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F29" s="18" t="str">
@@ -2170,15 +2476,15 @@
         <v/>
       </c>
       <c r="C30" s="15" t="str">
-        <f>IF(Groups!A8="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A8))</f>
+        <f>IF(Groups!A8="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A8))</f>
         <v/>
       </c>
       <c r="D30" s="15" t="str">
-        <f>IF(Groups!A8="","",SUMIF(Prompts!$B$4:$B$999,Groups!A8,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A8="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E30" s="15" t="str">
-        <f>IF(Groups!A8="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A8,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A8="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F30" s="18" t="str">
@@ -2196,15 +2502,15 @@
         <v/>
       </c>
       <c r="C31" s="15" t="str">
-        <f>IF(Groups!A9="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A9))</f>
+        <f>IF(Groups!A9="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A9))</f>
         <v/>
       </c>
       <c r="D31" s="15" t="str">
-        <f>IF(Groups!A9="","",SUMIF(Prompts!$B$4:$B$999,Groups!A9,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A9="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E31" s="15" t="str">
-        <f>IF(Groups!A9="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A9,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A9="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F31" s="18" t="str">
@@ -2222,15 +2528,15 @@
         <v/>
       </c>
       <c r="C32" s="15" t="str">
-        <f>IF(Groups!A10="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A10))</f>
+        <f>IF(Groups!A10="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A10))</f>
         <v/>
       </c>
       <c r="D32" s="15" t="str">
-        <f>IF(Groups!A10="","",SUMIF(Prompts!$B$4:$B$999,Groups!A10,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A10="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E32" s="15" t="str">
-        <f>IF(Groups!A10="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A10,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A10="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F32" s="18" t="str">
@@ -2248,15 +2554,15 @@
         <v/>
       </c>
       <c r="C33" s="15" t="str">
-        <f>IF(Groups!A11="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A11))</f>
+        <f>IF(Groups!A11="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A11))</f>
         <v/>
       </c>
       <c r="D33" s="15" t="str">
-        <f>IF(Groups!A11="","",SUMIF(Prompts!$B$4:$B$999,Groups!A11,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A11="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E33" s="15" t="str">
-        <f>IF(Groups!A11="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A11,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A11="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F33" s="18" t="str">
@@ -2274,15 +2580,15 @@
         <v/>
       </c>
       <c r="C34" s="15" t="str">
-        <f>IF(Groups!A12="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A12))</f>
+        <f>IF(Groups!A12="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A12))</f>
         <v/>
       </c>
       <c r="D34" s="15" t="str">
-        <f>IF(Groups!A12="","",SUMIF(Prompts!$B$4:$B$999,Groups!A12,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A12="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E34" s="15" t="str">
-        <f>IF(Groups!A12="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A12,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A12="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F34" s="18" t="str">
@@ -2300,15 +2606,15 @@
         <v/>
       </c>
       <c r="C35" s="15" t="str">
-        <f>IF(Groups!A13="","",COUNTIF(Prompts!$B$4:$B$999,Groups!A13))</f>
+        <f>IF(Groups!A13="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A13))</f>
         <v/>
       </c>
       <c r="D35" s="15" t="str">
-        <f>IF(Groups!A13="","",SUMIF(Prompts!$B$4:$B$999,Groups!A13,Prompts!$F$4:$F$999))</f>
+        <f>IF(Groups!A13="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
       <c r="E35" s="15" t="str">
-        <f>IF(Groups!A13="","",COUNTIFS(Prompts!$B$4:$B$999,Groups!A13,Prompts!$E$4:$E$999,"Success"))</f>
+        <f>IF(Groups!A13="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
       <c r="F35" s="18" t="str">

--- a/jira_clone/prompt_study.xlsx
+++ b/jira_clone/prompt_study.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maamoun\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57529FF3-DC37-4376-8F79-C6011EB582D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6976044-9F91-4B9C-882F-2FA257B6DB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="159">
   <si>
     <t>Prompt Study Workbook</t>
   </si>
@@ -696,6 +696,324 @@
   </si>
   <si>
     <t>Task 30</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>`in @force-app/main/default/classes/domain/TicketService.cls : 
+    //Todo create method removeTicketFromSprint
+     // Input : Ticket__c 
+        // call  decreaseTotalStoryPoint(ticket.Sprint__c, ticket.StoryPoint__c); 
+        // update the ticket.Sprint__c to null 
+     // Output : Sprint
+ and in @force-app/main/default/classes/controller/managebacklog/ManageBacklogController.cls : 
+    @AuraEnabled
+    public static APIResponse moveTicketToBacklog(String ticketId) {
+        try {
+            if (String.isBlank(ticketId)) return new APIResponse(false, 'ticketId is required');
+            Ticket__c existing = DomainCorrectness.requireTicketExists(ticketId);
+            // Todo call the created function  in the service removeTicketFromSprint
+            return new APIResponse(true, 'Ticket moved to backlog', updated);
+        } catch (Exception ex) {
+            return new APIResponse(false, 'Error moving ticket to backlog: ' + ex.getMessage());
+        }
+    }
+go with todos</t>
+  </si>
+  <si>
+    <t>Task 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">excellent </t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>in @force-app/main/default/classes/domain/TicketService.cls  : 
+     // Todo moveTicketToSprint : 
+      // Input : Ticket__c , Sprint__c 
+      // Logic : call increaseTotalStoryPoint and update Ticket Sprint id : without any validation 
+      // Output : return the updated Sprint 
+in @force-app/main/default/classes/controller/managebacklog/ManageBacklogController.cls  :  
+    @AuraEnabled
+    public static APIResponse moveTicketToSprint(String ticketId, String sprintId) {
+        try {
+            if (String.isBlank(ticketId)) return new APIResponse(false, 'ticketId is required');
+            if (String.isBlank(sprintId))  return new APIResponse(false, 'sprintId is required');
+            Sprint__c sprint = DomainCorrectness.requireSprintExists(sprintId);
+            Ticket__c existing = DomainCorrectness.requireTicketExists(ticketId);
+            // Todo call moveTicketToSprint and return the updated Sprint 
+            return new APIResponse(true, 'Ticket moved to sprint', updated);
+        } catch (Exception ex) {
+            return new APIResponse(false, 'Error moving ticket to sprint: ' + ex.getMessage());
+        }
+    }</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>in TicketService.moveTicketToSprint  before update the ticket.Sprint__c = sprint.Id : moveTicketToSprint we should call DomainCompleteValidator that ticket cannot move from sprint to another so throw a exception 
+@force-app/main/default/classes/domain/DomainCompleteValidator.cls</t>
+  </si>
+  <si>
+    <t>the reason that is high that I do not tell him where I should create increase method and it not exist before.</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">create a Dto class that include classes in it, exist in @force-app/main/default/classes/domain/  : 
+- CreateTicketResponse include createdTicket , updateSprint used in @force-app/main/default/classes/domain/TicketService.cls  for createTicket method line 28 . 
+the updated Sprint is from increaseTotalStoryPoint please do not validate wher ethis method exist and the return response .
+please do not validate if the method exist  just go to the line and you will find it. </t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>Task34</t>
+  </si>
+  <si>
+    <t>in @force-app/main/default/classes/domain/SprintService.cls   :     // Todo create increaseTotalEndStatus : 
+        // input : Sprint , story point 
+        // output : Sprint 
+in @force-app/main/default/classes/domain/TicketService.cls  : 
+public static Boolean changeTicketState(Ticket__c ticket, Status__c fromStatus, Status__c toStatus, List&lt;WorkflowTransition__c&gt; transitions) {
+        try {
+            DomainCompleteValidator.requireTransitionAllowed(fromStatus.Id, toStatus.Id, transitions);
+            ticket.CurrentState__c = toStatus.Id;
+            updateTicket(ticket);
+            // Todo check if the DomainCompleteValidator.isEndStatus(toStatus) : 
+                // Todo then increaseTotalEndStatus in SprintService 
+            // return changeTicketStateDto instead of boolean value  
+            return DomainCompleteValidator.isEndStatus(toStatus);
+        } catch (Exception ex) {
+            throw new ServiceException('Error changing ticket state: ' + ex.getMessage());
+        }
+    }
+in @force-app/main/default/classes/controller/manageTicketTracking/ManageTicketTrackingController.cls  :  update the  return of changeTicketState and in @force-app/main/default/classes/controller/manageTicketTracking/ManageTicketTrackingController.cls</t>
+  </si>
+  <si>
+    <t>update also change TicketState in @force-app/main/default/classes/controller/managebacklog/ManageBacklogController.cls</t>
+  </si>
+  <si>
+    <t>Task 36</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>P028</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>_callChangeTicketState(ticketId, fromStatusId, toStatusId) {
+        changeTicketState({ ticketId, fromStatusId, toStatusId })
+            .then(res =&gt; {
+                if (!res.success) { this.errorMessage = res.message; return; }
+                const isEndStatus = res.data &amp;&amp; res.data.isEndStatus;
+                const updatedSprint = null;
+                if(isEndStatus) { updatedSprint = res.data?.updatedSprint}
+                this._sprintTickets = this._sprintTickets.map(ticket =&gt;
+                    ticket.Id === ticketId
+                        ? {
+                            ...ticket,
+                            CurrentState__c: toStatusId,
+                            currentStatuses: this._statuses.find(s =&gt; s.statusId === toStatusId) || null,
+                            isEndStatus:     isEndStatus || false
+                          }
+                        : ticket
+                );
+                if (isEndStatus) {
+                    this.columns = this.columns.map(col =&gt; ({
+                        ...col,
+                        tickets: col.tickets.map(t =&gt;
+                            t.Id === ticketId
+                                ? { ...t, isEndStatus: true, _renderKey: t.Id + '_' + Date.now() }
+                                : t
+                        )
+                    }));
+                }
+            })
+            .catch(err =&gt; { this.errorMessage = (err.body &amp;&amp; err.body.message) || 'Error changing ticket state'; })
+    }
+update this method in the way that spread the ticket in enrichSprintTicketChangeState , 
+and for the case of isEndStatus : to update update the isEndStatus to true and renderkey change and alsoto enrich the sprint with a totalEndStorYpOINT , 
+so you can create a separate method called enrichSprintWithTicketStateChange that achieve the end status (change the method name to be reliable and easuy to understand )
+in @force-app/main/default/lwc/manageTicketTracking/manageTicketTracking.js</t>
+  </si>
+  <si>
+    <t>Task 37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in @force-app/main/default/lwc/manageBacklog/manageBacklog.js  in handleTicketStateChange when the response is came  get the  isEndStatus from data.isEndStatus and updatedSprint from data.updatedSprint however we get the data.updatedSprint in the case when  the isEndStatus is true . 
+so in the case of isEndStatus true get the totalEndedStoryPoint from it and enrich the current sprint with it this if the ticket have a sprint </t>
+  </si>
+  <si>
+    <t># Use Case Specifications: Create Ticket
+---
+	## Use Case 1: Create Ticket from Backlog
+		### Actor
+		Project Member (authenticated user with access to the project's backlog)
+		### Front-End Pre-conditions
+		- User is authenticated and logged into the application.
+		- User has navigated to the **Backlog** view of a project.
+		- User is an active member of the project.
+		- The project's ticket types, statuses, and members are already loaded in the UI.
+		### Trigger
+		User clicks the **"Create Ticket"** button on the Backlog page, which opens the ticket creation form/modal.
+		### Front-End Validation
+		Before sending the request, the front-end validates:
+		- `name` is not empty.
+		- `summary` is not empty.
+		- `ticketTypeId` is selected from the dropdown.
+		- `storyPoint` (if provided) is a positive integer.
+		- `priority` (if provided) is one of the allowed values (`Low`, `Medium`, `High`).
+		- If any validation fails → display inline error messages on the form fields; the request is **not** sent.
+		### Request — Backend Method Call
+		**Endpoint:** `POST /services/apexrest/tickets`  
+		**Backend Method:** `TicketController.createTicket(...)`
+		**Request Body:**
+		```json
+		{
+		  "name": "TICK-001",
+		  "summary": "Implement login validation",
+		  "ticketTypeId": "a01XXXXXXXXXXXX",
+		  "currentStateId": null,
+		  "description": "Add client-side validation for the login form",
+		  "storyPoint": 5,
+		  "assignedToId": "a03XXXXXXXXXXXX",
+		  "epicId": "a04XXXXXXXXXXXX",
+		  "sprintId": null,
+		  "priority": "Medium"
+		}
+		```
+		### Response Handling
+		#### Success Case
+		- Backend returns `APIResponse(success = true, message = "Ticket created successfully", data = { createdTicket })`.
+		- Front-end:
+		  - Closes the creation modal.
+		  - Displays a success toast: *"Ticket created successfully."*
+		  - Appends the new ticket card to the Backlog list (no sprint refresh needed).
+		#### Failure — Front-End Validation Failure
+		- The request is never sent.
+		- Inline error messages are displayed under the invalid form fields.
+		- The "Create" button remains disabled or re-enabled depending on input correction.
+		#### Failure — Back-End Failure
+		- Backend returns `APIResponse(success = false, message = "&lt;error reason&gt;")`.
+		- Possible reasons:
+		  - Missing required fields (`name`, `summary`, `ticketTypeId`).
+		  - Ticket type does not exist.
+		  - Assigned member is not active.
+		  - Epic is not active.
+		  - Current user is not a member of the project.
+		  - DML / unexpected server exception.
+		- Front-end:
+		  - Keeps the modal open with the user's input preserved.
+		  - Displays an error toast or banner with the returned message.
+		### Post-conditions
+		- A new `Ticket__c` record exists with `RecordStatus__c = 'active'`.
+		- The ticket is not linked to any sprint.
+		- No sprint record is modified.
+		---
+	## Use Case 2: Create Ticket from Sprint
+		### Actor
+		Project Member (authenticated user with access to an active sprint)
+		### Front-End Pre-conditions
+		- User is authenticated and logged into the application.
+		- User has navigated to a **Sprint** view (Sprint board or Sprint backlog).
+		- The selected sprint exists.
+		- User is an active member of the project owning the sprint.
+		- Project ticket types, statuses, members, and the current sprint context are loaded in the UI.
+		### Trigger
+		User clicks the **"Create Ticket"** button from within the Sprint view (Sprint board or Sprint backlog), which opens the ticket creation form/modal with the current `sprintId` pre-filled.
+		### Front-End Validation
+		Before sending the request, the front-end validates:
+		- `name` is not empty.
+		- `summary` is not empty.
+		- `ticketTypeId` is selected from the dropdown.
+		- `sprintId` is present (auto-filled from context — should never be empty in this flow).
+		- `storyPoint` (if provided) is a positive integer.
+		- `priority` (if provided) is one of the allowed values (`Low`, `Medium`, `High`).
+		- If any validation fails → display inline error messages; the request is **not** sent.
+		### Request — Backend Method Call
+		**Endpoint:** `POST /services/apexrest/tickets`  
+		**Backend Method:** `TicketController.createTicket(...)`
+		**Request Body:**
+		```json
+		{
+		  "name": "TICK-002",
+		  "summary": "Fix payment gateway timeout",
+		  "ticketTypeId": "a01XXXXXXXXXXXX",
+		  "currentStateId": "a02XXXXXXXXXXXX",
+		  "description": "Increase timeout threshold for the payment API",
+		  "storyPoint": 3,
+		  "assignedToId": "a03XXXXXXXXXXXX",
+		  "epicId": "a04XXXXXXXXXXXX",
+		  "sprintId": "a05XXXXXXXXXXXX",
+		  "priority": "High"
+		}
+		```
+		### Response Handling
+		#### Success Case
+		- Backend returns `APIResponse(success = true, message = "Ticket created successfully", data = { createdTicket, updatedSprint })`.
+		- Front-end:
+		  - Closes the creation modal.
+		  - Displays a success toast: *"Ticket created successfully."*
+		  - Adds the new ticket card to the Sprint board / Sprint backlog.
+		  - Updates the sprint's displayed `totalStoryPoint` (and `endedStoryPoint` if the ticket was created already in an end status) using the `updatedSprint` returned from the backend.
+		#### Failure — Front-End Validation Failure
+		- The request is never sent.
+		- Inline error messages are displayed under the invalid form fields.
+		- The "Create" button stays disabled or re-enabled depending on input correction.
+		#### Failure — Back-End Failure
+		- Backend returns `APIResponse(success = false, message = "&lt;error reason&gt;")`.
+		- Possible reasons:
+		  - Missing required fields (`name`, `summary`, `ticketTypeId`).
+		  - Ticket type does not exist.
+		  - Sprint does not exist.
+		  - Assigned member is not active.
+		  - Epic is not active.
+		  - Current user is not a member of the project.
+		  - DML / unexpected server exception.
+		- Front-end:
+		  - Keeps the modal open with the user's input preserved.
+		  - Displays an error toast or banner with the returned message.
+		  - Does **not** update the sprint's story-point totals on the UI.
+		### Post-conditions
+		- A new `Ticket__c` record exists with `RecordStatus__c = 'active'` and `Sprint__c` set to the current sprint.
+		- The sprint's `totalStoryPoint` is increased by the ticket's `storyPoint`.
+		- If the ticket was created already in an **end status**, the sprint's `endedStoryPoint` is also increased by the ticket's `storyPoint`.
+	---
+	## Quick Comparison
+	| Aspect | Backlog | Sprint |
+	|---|---|---|
+	| Entry point | Backlog view | Sprint view |
+	| `sprintId` in request | `null` | Populated |
+	| Back-end sprint existence check | Skipped | Executes |
+	| Sprint story-point update | None | `totalStoryPoint` (+ `endedStoryPoint` if end status) |
+	| Response payload | `createdTicket` | `createdTicket` + `updatedSprint` |
+	| UI side effect on success | Add card to Backlog | Add card to Sprint + refresh sprint metrics |</t>
+  </si>
+  <si>
+    <t>Claude oPUS</t>
+  </si>
+  <si>
+    <t>EXCELLENT</t>
+  </si>
+  <si>
+    <t>TASK 41</t>
+  </si>
+  <si>
+    <t>P029</t>
   </si>
 </sst>
 </file>
@@ -828,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -856,7 +1174,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -894,12 +1211,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1370,11 +1699,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="5"/>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>87</v>
       </c>
       <c r="D5" s="6"/>
@@ -1549,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1613,7 +1942,7 @@
       <c r="E4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="20" t="s">
         <v>72</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -1640,7 +1969,7 @@
       <c r="F5" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>73</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -1657,83 +1986,83 @@
       <c r="C6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>77</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>72</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="204" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>79</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="132" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>83</v>
       </c>
       <c r="E9" s="8"/>
@@ -1742,14 +2071,14 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="5"/>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>84</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -1764,14 +2093,14 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>85</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="5"/>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>88</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -1813,7 +2142,7 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="21" t="s">
         <v>94</v>
       </c>
       <c r="E13" s="8" t="s">
@@ -1821,7 +2150,7 @@
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="19" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1833,27 +2162,27 @@
       <c r="C14" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>52</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="19" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1861,29 +2190,29 @@
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="394.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>100</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="20" t="s">
         <v>111</v>
       </c>
       <c r="G16" s="8"/>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="19" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1893,17 +2222,17 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="20" t="s">
         <v>86</v>
       </c>
       <c r="G17" s="8"/>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="19" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1913,7 +2242,7 @@
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="23" t="s">
         <v>107</v>
       </c>
       <c r="E18" s="8"/>
@@ -1927,39 +2256,39 @@
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="23" t="s">
         <v>103</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>86</v>
+      <c r="F19" s="20" t="s">
+        <v>140</v>
       </c>
       <c r="G19" s="8"/>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="18" t="s">
         <v>110</v>
       </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="24" t="s">
         <v>109</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="20" t="s">
         <v>86</v>
       </c>
       <c r="G20" s="8"/>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="19" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1971,7 +2300,7 @@
       <c r="C21" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E21" s="8" t="s">
@@ -1992,120 +2321,311 @@
         <v>119</v>
       </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="19" t="s">
+      <c r="F22" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="H22" s="20" t="s">
+      <c r="H22" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>127</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>128</v>
       </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>121</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G24" s="19" t="s">
+      <c r="F24" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="18" t="s">
         <v>129</v>
       </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="19" t="s">
         <v>122</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="19" t="s">
+      <c r="F25" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G25" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="H25" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F26" s="11"/>
+      <c r="A26" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F27" s="11"/>
+      <c r="A27" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F28" s="11"/>
+      <c r="A28" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="8"/>
+      <c r="C28" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F29" s="11"/>
+      <c r="A29" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F30" s="11"/>
+      <c r="A30" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F31" s="11"/>
+      <c r="A31" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="32" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F32" s="11"/>
-    </row>
-    <row r="33" spans="6:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F33" s="11"/>
+      <c r="A32" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="31" t="s">
+        <v>156</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2165,75 +2685,75 @@
       <c r="C3" s="26"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <f>COUNTA(Prompts!A4:A1000)</f>
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <f>COUNTA(Groups!A4:A50)</f>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <f>SUM(Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
         <f>IFERROR(SUM(Prompts!F4:F1000)/COUNTIF(Prompts!F4:F1000,"&gt;0"),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <f>IFERROR(MAX(Prompts!F4:F1000),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <f>IFERROR(SMALL(Prompts!F4:F1000,COUNTIF(Prompts!F4:F1000,0)+1),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Success")/COUNTA(Prompts!A4:A1000),0)</f>
-        <v>0.77272727272727271</v>
+        <v>0.83870967741935487</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <f>IFERROR(COUNTIF(Prompts!E4:E1000,"Failed")/COUNTA(Prompts!A4:A1000),0)</f>
-        <v>0.13636363636363635</v>
+        <v>9.6774193548387094E-2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -2258,11 +2778,11 @@
       <c r="A16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <f>COUNTIF(Prompts!E4:E1000,A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f>SUMIF(Prompts!E4:E1000,A16,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
@@ -2271,11 +2791,11 @@
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <f>COUNTIF(Prompts!E4:E1000,A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <f>SUMIF(Prompts!E4:E1000,A17,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
@@ -2284,11 +2804,11 @@
       <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <f>COUNTIF(Prompts!E4:E1000,A18)</f>
-        <v>17</v>
-      </c>
-      <c r="C18" s="15">
+        <v>26</v>
+      </c>
+      <c r="C18" s="14">
         <f>SUMIF(Prompts!E4:E1000,A18,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
@@ -2297,11 +2817,11 @@
       <c r="A19" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <f>COUNTIF(Prompts!E4:E1000,A19)</f>
         <v>3</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <f>SUMIF(Prompts!E4:E1000,A19,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
@@ -2310,24 +2830,24 @@
       <c r="A20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <f>COUNTIF(Prompts!E4:E1000,A20)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <f>SUMIF(Prompts!E4:E1000,A20,Prompts!F4:F1000)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <f>SUM(B16:B20)</f>
-        <v>20</v>
-      </c>
-      <c r="C21" s="17">
+        <v>29</v>
+      </c>
+      <c r="C21" s="16">
         <f>SUM(C16:C20)</f>
         <v>0</v>
       </c>
@@ -2371,19 +2891,19 @@
         <f>IF(Groups!A4="","",Groups!B4)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <f>IF(Groups!A4="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A4))</f>
         <v>3</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <f>IF(Groups!A4="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$F$4:$F$1000))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="14">
         <f>IF(Groups!A4="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A4,Prompts!$E$4:$E$1000,"Success"))</f>
         <v>3</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="17">
         <f t="shared" ref="F26:F35" si="0">IFERROR(E26/C26,"")</f>
         <v>1</v>
       </c>
@@ -2397,19 +2917,19 @@
         <f>IF(Groups!A5="","",Groups!B5)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <f>IF(Groups!A5="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A5))</f>
         <v>3</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <f>IF(Groups!A5="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$F$4:$F$1000))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="14">
         <f>IF(Groups!A5="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A5,Prompts!$E$4:$E$1000,"Success"))</f>
         <v>2</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="17">
         <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
@@ -2423,19 +2943,19 @@
         <f>IF(Groups!A6="","",Groups!B6)</f>
         <v/>
       </c>
-      <c r="C28" s="15" t="str">
+      <c r="C28" s="14" t="str">
         <f>IF(Groups!A6="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A6))</f>
         <v/>
       </c>
-      <c r="D28" s="15" t="str">
+      <c r="D28" s="14" t="str">
         <f>IF(Groups!A6="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E28" s="15" t="str">
+      <c r="E28" s="14" t="str">
         <f>IF(Groups!A6="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A6,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F28" s="18" t="str">
+      <c r="F28" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2449,19 +2969,19 @@
         <f>IF(Groups!A7="","",Groups!B7)</f>
         <v/>
       </c>
-      <c r="C29" s="15" t="str">
+      <c r="C29" s="14" t="str">
         <f>IF(Groups!A7="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A7))</f>
         <v/>
       </c>
-      <c r="D29" s="15" t="str">
+      <c r="D29" s="14" t="str">
         <f>IF(Groups!A7="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E29" s="15" t="str">
+      <c r="E29" s="14" t="str">
         <f>IF(Groups!A7="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A7,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F29" s="18" t="str">
+      <c r="F29" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2475,19 +2995,19 @@
         <f>IF(Groups!A8="","",Groups!B8)</f>
         <v/>
       </c>
-      <c r="C30" s="15" t="str">
+      <c r="C30" s="14" t="str">
         <f>IF(Groups!A8="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A8))</f>
         <v/>
       </c>
-      <c r="D30" s="15" t="str">
+      <c r="D30" s="14" t="str">
         <f>IF(Groups!A8="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E30" s="15" t="str">
+      <c r="E30" s="14" t="str">
         <f>IF(Groups!A8="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A8,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F30" s="18" t="str">
+      <c r="F30" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2501,19 +3021,19 @@
         <f>IF(Groups!A9="","",Groups!B9)</f>
         <v/>
       </c>
-      <c r="C31" s="15" t="str">
+      <c r="C31" s="14" t="str">
         <f>IF(Groups!A9="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A9))</f>
         <v/>
       </c>
-      <c r="D31" s="15" t="str">
+      <c r="D31" s="14" t="str">
         <f>IF(Groups!A9="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E31" s="15" t="str">
+      <c r="E31" s="14" t="str">
         <f>IF(Groups!A9="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A9,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F31" s="18" t="str">
+      <c r="F31" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2527,19 +3047,19 @@
         <f>IF(Groups!A10="","",Groups!B10)</f>
         <v/>
       </c>
-      <c r="C32" s="15" t="str">
+      <c r="C32" s="14" t="str">
         <f>IF(Groups!A10="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A10))</f>
         <v/>
       </c>
-      <c r="D32" s="15" t="str">
+      <c r="D32" s="14" t="str">
         <f>IF(Groups!A10="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E32" s="15" t="str">
+      <c r="E32" s="14" t="str">
         <f>IF(Groups!A10="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A10,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F32" s="18" t="str">
+      <c r="F32" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2553,19 +3073,19 @@
         <f>IF(Groups!A11="","",Groups!B11)</f>
         <v/>
       </c>
-      <c r="C33" s="15" t="str">
+      <c r="C33" s="14" t="str">
         <f>IF(Groups!A11="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A11))</f>
         <v/>
       </c>
-      <c r="D33" s="15" t="str">
+      <c r="D33" s="14" t="str">
         <f>IF(Groups!A11="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E33" s="15" t="str">
+      <c r="E33" s="14" t="str">
         <f>IF(Groups!A11="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A11,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F33" s="18" t="str">
+      <c r="F33" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2579,19 +3099,19 @@
         <f>IF(Groups!A12="","",Groups!B12)</f>
         <v/>
       </c>
-      <c r="C34" s="15" t="str">
+      <c r="C34" s="14" t="str">
         <f>IF(Groups!A12="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A12))</f>
         <v/>
       </c>
-      <c r="D34" s="15" t="str">
+      <c r="D34" s="14" t="str">
         <f>IF(Groups!A12="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E34" s="15" t="str">
+      <c r="E34" s="14" t="str">
         <f>IF(Groups!A12="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A12,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F34" s="18" t="str">
+      <c r="F34" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -2605,19 +3125,19 @@
         <f>IF(Groups!A13="","",Groups!B13)</f>
         <v/>
       </c>
-      <c r="C35" s="15" t="str">
+      <c r="C35" s="14" t="str">
         <f>IF(Groups!A13="","",COUNTIF(Prompts!$B$4:$B$1000,Groups!A13))</f>
         <v/>
       </c>
-      <c r="D35" s="15" t="str">
+      <c r="D35" s="14" t="str">
         <f>IF(Groups!A13="","",SUMIF(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$F$4:$F$1000))</f>
         <v/>
       </c>
-      <c r="E35" s="15" t="str">
+      <c r="E35" s="14" t="str">
         <f>IF(Groups!A13="","",COUNTIFS(Prompts!$B$4:$B$1000,Groups!A13,Prompts!$E$4:$E$1000,"Success"))</f>
         <v/>
       </c>
-      <c r="F35" s="18" t="str">
+      <c r="F35" s="17" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
